--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>39684.17</v>
+        <v>40045.88</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>19606.99</v>
+        <v>19740.59</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12632.89</v>
+        <v>12457.32</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>36524</v>
+        <v>37425.15</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>63155.28</v>
+        <v>61806.72</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>386079.54</v>
+        <v>388618.51</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>30140.81</v>
+        <v>30383.54</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057539-29772-CM25</t>
+          <t>2307-2925-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>40045.88</v>
+        <v>167401.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>450-630-CM25</t>
+          <t>1057539-29772-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.210.300-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>19740.59</v>
+        <v>40045.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2328-9-CM26</t>
+          <t>450-630-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.210.300-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>ZECOVERY LTDA   -    EXEC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12457.32</v>
+        <v>19740.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5413-88-CM26</t>
+          <t>2328-9-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>VICTORIA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>37425.15</v>
+        <v>12457.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1393093-359-CM26</t>
+          <t>5413-88-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>61806.72</v>
+        <v>37425.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057539-2804-CM26</t>
+          <t>1393093-359-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>ANDESTIC SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>388618.51</v>
+        <v>61806.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1662-1064-CM26</t>
+          <t>1057539-2804-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.602.273-3</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,6 +935,67 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
+        <v>388618.51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1662-1064-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.602.273-3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Servicio de Salud del Reloncaví</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>GEORG</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>30383.54</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2307-2925-CM25</t>
+          <t>5413-5-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>167401.82</v>
+        <v>31499.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057539-29772-CM25</t>
+          <t>2328-26-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>40045.88</v>
+        <v>8852.549999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>450-630-CM25</t>
+          <t>1057539-8836-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.210.300-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>19740.59</v>
+        <v>29569.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2328-9-CM26</t>
+          <t>1057539-16153-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12457.32</v>
+        <v>58749.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5413-88-CM26</t>
+          <t>1057539-16834-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>37425.15</v>
+        <v>36693.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1393093-359-CM26</t>
+          <t>2307-2925-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>61806.72</v>
+        <v>167401.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057539-2804-CM26</t>
+          <t>5413-533-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>388618.51</v>
+        <v>69696.74000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1662-1064-CM26</t>
+          <t>1057539-20176-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.602.273-3</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,7 +996,739 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>63154.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1057539-20177-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>56727.35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1057539-20625-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>62924.68</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>752-364-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>72.221.800-0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>62422.76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2307-3666-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>34816.93</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1057539-29772-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>40045.88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>450-630-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.210.300-9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ZECOVERY LTDA   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>19740.59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2328-9-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>VICTORIA SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>12457.32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5413-88-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>37425.15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1393093-359-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.981.360-K</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ANDESTIC SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.031.392-0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>61806.72</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1057539-2804-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>388618.51</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1662-1064-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.602.273-3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Servicio de Salud del Reloncaví</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>GEORG</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>30383.54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1393093-673-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.981.360-K</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.213.064-5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>42005.51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>VICTORIA S.A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1057539-20176-CM25</t>
+          <t>1057539-20177-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>63154.4</v>
+        <v>56727.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057539-20177-CM25</t>
+          <t>1057539-20176-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>56727.35</v>
+        <v>63154.4</v>
       </c>
     </row>
     <row r="11">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1729,6 +1729,128 @@
       </c>
       <c r="M21" s="2" t="n">
         <v>42005.51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>608897-244-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.979.930-5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.185.219-1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>24415.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1393093-777-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.981.360-K</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>26162.38</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
@@ -562,7 +562,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1184,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1371,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1436,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1501,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1688,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1875,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VICTORIA S.A</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-lagos.xlsx
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
